--- a/scraper/downloads/yad2_page_5.xlsx
+++ b/scraper/downloads/yad2_page_5.xlsx
@@ -333,31 +333,38 @@
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t xml:space="preserve">נגבה</t>
+          <t xml:space="preserve">משמר העם</t>
         </is>
       </c>
       <c r="D3" s="65">
         <v>16</v>
       </c>
-      <c r="E3" s="65">
-        <v>0</v>
+      <c t="inlineStr" r="E3">
+        <is>
+          <t xml:space="preserve">/32</t>
+        </is>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">דופלקס</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G3" s="65">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">111מ״ר</t>
+          <t xml:space="preserve">346מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I3">
+        <is>
+          <t xml:space="preserve">מרפסת: 45מ״רגינה: 74מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K3">
@@ -365,22 +372,17 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="N3">
-        <is>
-          <t xml:space="preserve">נדב - מתווך(052) 698-4466</t>
-        </is>
-      </c>
       <c r="O3" s="63">
-        <v>5500000</v>
+        <v>26500000</v>
       </c>
       <c t="inlineStr" r="R3">
         <is>
-          <t xml:space="preserve">פעיל</t>
+          <t xml:space="preserve">הרשמה</t>
         </is>
       </c>
       <c t="inlineStr" r="S3">
         <is>
-          <t xml:space="preserve">מנחם אוריאל12-02-2026</t>
+          <t xml:space="preserve">אורן כהן05-08-2024</t>
         </is>
       </c>
     </row>
@@ -399,14 +401,14 @@
         </is>
       </c>
       <c r="D4" s="65">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E4" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F4">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דופלקס</t>
         </is>
       </c>
       <c r="G4" s="65">
@@ -414,12 +416,7 @@
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">88מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I4">
-        <is>
-          <t xml:space="preserve">גינה: 68מ״ר</t>
+          <t xml:space="preserve">111מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
@@ -434,11 +431,11 @@
       </c>
       <c t="inlineStr" r="N4">
         <is>
-          <t xml:space="preserve">נייל15165891551</t>
+          <t xml:space="preserve">נדב - מתווך(052) 698-4466</t>
         </is>
       </c>
       <c r="O4" s="63">
-        <v>4550000</v>
+        <v>5500000</v>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -447,7 +444,7 @@
       </c>
       <c t="inlineStr" r="S4">
         <is>
-          <t xml:space="preserve">רבקה בן זקן19-05-2025</t>
+          <t xml:space="preserve">מנחם אוריאל12-02-2026</t>
         </is>
       </c>
     </row>
@@ -462,26 +459,31 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">נחלת צדוק</t>
+          <t xml:space="preserve">נגבה</t>
         </is>
       </c>
       <c r="D5" s="65">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E5" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F5">
         <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c t="n" r="G5">
-        <v>5.5</v>
+          <t xml:space="preserve">דירת גן</t>
+        </is>
+      </c>
+      <c r="G5" s="65">
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">580מ״ר</t>
+          <t xml:space="preserve">88מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I5">
+        <is>
+          <t xml:space="preserve">גינה: 68מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
@@ -496,11 +498,11 @@
       </c>
       <c t="inlineStr" r="N5">
         <is>
-          <t xml:space="preserve">דוד גז</t>
-        </is>
-      </c>
-      <c r="O5" s="65">
-        <v>0</v>
+          <t xml:space="preserve">נייל15165891551</t>
+        </is>
+      </c>
+      <c r="O5" s="63">
+        <v>4550000</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -509,7 +511,7 @@
       </c>
       <c t="inlineStr" r="S5">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">רבקה בן זקן19-05-2025</t>
         </is>
       </c>
     </row>
@@ -528,27 +530,22 @@
         </is>
       </c>
       <c r="D6" s="65">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E6" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F6">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
-        </is>
-      </c>
-      <c r="G6" s="65">
-        <v>10</v>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="n" r="G6">
+        <v>5.5</v>
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">489מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I6">
-        <is>
-          <t xml:space="preserve">גינה: 80מ״ר</t>
+          <t xml:space="preserve">580מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
@@ -561,18 +558,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L6">
-        <is>
-          <t xml:space="preserve">צפון דרום</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N6">
         <is>
-          <t xml:space="preserve">שפיגלר</t>
-        </is>
-      </c>
-      <c r="O6" s="63">
-        <v>50000000</v>
+          <t xml:space="preserve">דוד גז</t>
+        </is>
+      </c>
+      <c r="O6" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R6">
         <is>
@@ -581,7 +573,7 @@
       </c>
       <c t="inlineStr" r="S6">
         <is>
-          <t xml:space="preserve">אורן כהן26-08-2024</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -600,7 +592,7 @@
         </is>
       </c>
       <c r="D7" s="65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E7" s="65">
         <v>0</v>
@@ -615,12 +607,12 @@
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">580מ״ר</t>
+          <t xml:space="preserve">489מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I7">
         <is>
-          <t xml:space="preserve">גינה: 140מ״ר</t>
+          <t xml:space="preserve">גינה: 80מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J7">
@@ -640,11 +632,11 @@
       </c>
       <c t="inlineStr" r="N7">
         <is>
-          <t xml:space="preserve">עמי(054) 398-4981</t>
+          <t xml:space="preserve">שפיגלר</t>
         </is>
       </c>
       <c r="O7" s="63">
-        <v>55000000</v>
+        <v>50000000</v>
       </c>
       <c t="inlineStr" r="R7">
         <is>
@@ -653,7 +645,7 @@
       </c>
       <c t="inlineStr" r="S7">
         <is>
-          <t xml:space="preserve">אורן כהן27-10-2024</t>
+          <t xml:space="preserve">אורן כהן26-08-2024</t>
         </is>
       </c>
     </row>
@@ -668,26 +660,31 @@
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">נחלת צדוק 13</t>
+          <t xml:space="preserve">נחלת צדוק</t>
         </is>
       </c>
       <c r="D8" s="65">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E8" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F8">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">בית פרטי</t>
         </is>
       </c>
       <c r="G8" s="65">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">400מ״ר</t>
+          <t xml:space="preserve">580מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I8">
+        <is>
+          <t xml:space="preserve">גינה: 140מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
@@ -700,8 +697,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L8">
+        <is>
+          <t xml:space="preserve">צפון דרום</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="N8">
+        <is>
+          <t xml:space="preserve">עמי(054) 398-4981</t>
+        </is>
+      </c>
       <c r="O8" s="63">
-        <v>36000000</v>
+        <v>55000000</v>
       </c>
       <c t="inlineStr" r="R8">
         <is>
@@ -710,7 +717,7 @@
       </c>
       <c t="inlineStr" r="S8">
         <is>
-          <t xml:space="preserve">רבקה בן זקן10-03-2026</t>
+          <t xml:space="preserve">אורן כהן27-10-2024</t>
         </is>
       </c>
     </row>
@@ -725,16 +732,14 @@
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">נפתלי</t>
+          <t xml:space="preserve">נחלת צדוק 13</t>
         </is>
       </c>
       <c r="D9" s="65">
-        <v>23</v>
-      </c>
-      <c t="inlineStr" r="E9">
-        <is>
-          <t xml:space="preserve">/50</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E9" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F9">
         <is>
@@ -742,16 +747,11 @@
         </is>
       </c>
       <c r="G9" s="65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">93מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I9">
-        <is>
-          <t xml:space="preserve">מרפסת: 3מ״ר</t>
+          <t xml:space="preserve">400מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
@@ -764,13 +764,8 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="N9">
-        <is>
-          <t xml:space="preserve">רוני דוד(050) 750-1598</t>
-        </is>
-      </c>
       <c r="O9" s="63">
-        <v>4000000</v>
+        <v>36000000</v>
       </c>
       <c t="inlineStr" r="R9">
         <is>
@@ -779,7 +774,7 @@
       </c>
       <c t="inlineStr" r="S9">
         <is>
-          <t xml:space="preserve">אלחנן רווח03-12-2024</t>
+          <t xml:space="preserve">רבקה בן זקן10-03-2026</t>
         </is>
       </c>
     </row>
@@ -794,14 +789,16 @@
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">נרקיס</t>
+          <t xml:space="preserve">נפתלי</t>
         </is>
       </c>
       <c r="D10" s="65">
-        <v>9</v>
-      </c>
-      <c r="E10" s="65">
-        <v>0</v>
+        <v>23</v>
+      </c>
+      <c t="inlineStr" r="E10">
+        <is>
+          <t xml:space="preserve">/50</t>
+        </is>
       </c>
       <c t="inlineStr" r="F10">
         <is>
@@ -809,21 +806,21 @@
         </is>
       </c>
       <c r="G10" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">87מ״ר</t>
+          <t xml:space="preserve">93מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
         <is>
-          <t xml:space="preserve">גינה: 31.95מ״ר</t>
+          <t xml:space="preserve">מרפסת: 3מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K10">
@@ -833,11 +830,11 @@
       </c>
       <c t="inlineStr" r="N10">
         <is>
-          <t xml:space="preserve">זכריה מוקטון (מתווך)058-7925395</t>
+          <t xml:space="preserve">רוני דוד(050) 750-1598</t>
         </is>
       </c>
       <c r="O10" s="63">
-        <v>6300000</v>
+        <v>4000000</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -846,7 +843,7 @@
       </c>
       <c t="inlineStr" r="S10">
         <is>
-          <t xml:space="preserve">מנחם אוריאל12-02-2026</t>
+          <t xml:space="preserve">אלחנן רווח03-12-2024</t>
         </is>
       </c>
     </row>
@@ -861,11 +858,11 @@
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">סוקולוב</t>
+          <t xml:space="preserve">נרקיס</t>
         </is>
       </c>
       <c r="D11" s="65">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E11" s="65">
         <v>0</v>
@@ -876,16 +873,21 @@
         </is>
       </c>
       <c r="G11" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">110מ״ר</t>
+          <t xml:space="preserve">87מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I11">
+        <is>
+          <t xml:space="preserve">גינה: 31.95מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K11">
@@ -895,11 +897,11 @@
       </c>
       <c t="inlineStr" r="N11">
         <is>
-          <t xml:space="preserve">יותם בר עמי(054) 462-2020</t>
-        </is>
-      </c>
-      <c r="O11" s="65">
-        <v>0</v>
+          <t xml:space="preserve">זכריה מוקטון (מתווך)058-7925395</t>
+        </is>
+      </c>
+      <c r="O11" s="63">
+        <v>6300000</v>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -908,7 +910,7 @@
       </c>
       <c t="inlineStr" r="S11">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">מנחם אוריאל12-02-2026</t>
         </is>
       </c>
     </row>
@@ -923,11 +925,11 @@
       </c>
       <c t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">סמאטס</t>
+          <t xml:space="preserve">סוקולוב</t>
         </is>
       </c>
       <c r="D12" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="65">
         <v>0</v>
@@ -938,16 +940,11 @@
         </is>
       </c>
       <c r="G12" s="65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">790מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I12">
-        <is>
-          <t xml:space="preserve">מרפסת: 160מ״ר</t>
+          <t xml:space="preserve">110מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
@@ -962,7 +959,7 @@
       </c>
       <c t="inlineStr" r="N12">
         <is>
-          <t xml:space="preserve">לא בשוק</t>
+          <t xml:space="preserve">יותם בר עמי(054) 462-2020</t>
         </is>
       </c>
       <c r="O12" s="65">
@@ -975,7 +972,7 @@
       </c>
       <c t="inlineStr" r="S12">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -990,16 +987,14 @@
       </c>
       <c t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">סמולןסקין</t>
+          <t xml:space="preserve">סמאטס</t>
         </is>
       </c>
       <c r="D13" s="65">
-        <v>1</v>
-      </c>
-      <c t="inlineStr" r="E13">
-        <is>
-          <t xml:space="preserve">/42</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="E13" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F13">
         <is>
@@ -1007,16 +1002,16 @@
         </is>
       </c>
       <c r="G13" s="65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">83מ״ר</t>
+          <t xml:space="preserve">790מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I13">
         <is>
-          <t xml:space="preserve">מרפסת: 3מ״ר</t>
+          <t xml:space="preserve">מרפסת: 160מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
@@ -1029,18 +1024,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L13">
-        <is>
-          <t xml:space="preserve">מזרח</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N13">
         <is>
-          <t xml:space="preserve">עמית050-476-1195</t>
-        </is>
-      </c>
-      <c r="O13" s="63">
-        <v>6000000</v>
+          <t xml:space="preserve">לא בשוק</t>
+        </is>
+      </c>
+      <c r="O13" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R13">
         <is>
@@ -1049,7 +1039,7 @@
       </c>
       <c t="inlineStr" r="S13">
         <is>
-          <t xml:space="preserve">דוב רבינובץ\'13-05-2026</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1064,26 +1054,33 @@
       </c>
       <c t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">עובד</t>
+          <t xml:space="preserve">סמולןסקין</t>
         </is>
       </c>
       <c r="D14" s="65">
-        <v>11</v>
-      </c>
-      <c r="E14" s="65">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c t="inlineStr" r="E14">
+        <is>
+          <t xml:space="preserve">/42</t>
+        </is>
       </c>
       <c t="inlineStr" r="F14">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G14" s="65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">1700מ״ר</t>
+          <t xml:space="preserve">83מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I14">
+        <is>
+          <t xml:space="preserve">מרפסת: 3מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
@@ -1096,13 +1093,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L14">
+        <is>
+          <t xml:space="preserve">מזרח</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N14">
         <is>
-          <t xml:space="preserve">מתי(054) 334-4386</t>
+          <t xml:space="preserve">עמית050-476-1195</t>
         </is>
       </c>
       <c r="O14" s="63">
-        <v>35000000</v>
+        <v>6000000</v>
       </c>
       <c t="inlineStr" r="R14">
         <is>
@@ -1111,7 +1113,7 @@
       </c>
       <c t="inlineStr" r="S14">
         <is>
-          <t xml:space="preserve">אין שיוך לאיש מכירות04-11-2024</t>
+          <t xml:space="preserve">דוב רבינובץ\'13-05-2026</t>
         </is>
       </c>
     </row>
@@ -1126,31 +1128,26 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">עובדיה מברטנורא</t>
+          <t xml:space="preserve">עובד</t>
         </is>
       </c>
       <c r="D15" s="65">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E15" s="65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F15">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">בית פרטי</t>
         </is>
       </c>
       <c r="G15" s="65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">80מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I15">
-        <is>
-          <t xml:space="preserve">מרפסת: 6מ״ר</t>
+          <t xml:space="preserve">1700מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
@@ -1165,11 +1162,11 @@
       </c>
       <c t="inlineStr" r="N15">
         <is>
-          <t xml:space="preserve">דני נמדר</t>
+          <t xml:space="preserve">מתי(054) 334-4386</t>
         </is>
       </c>
       <c r="O15" s="63">
-        <v>4100000</v>
+        <v>35000000</v>
       </c>
       <c t="inlineStr" r="R15">
         <is>
@@ -1178,7 +1175,7 @@
       </c>
       <c t="inlineStr" r="S15">
         <is>
-          <t xml:space="preserve">אין שיוך לאיש מכירות15-02-2026</t>
+          <t xml:space="preserve">אין שיוך לאיש מכירות04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1193,31 +1190,31 @@
       </c>
       <c t="inlineStr" r="C16">
         <is>
-          <t xml:space="preserve">עזה</t>
+          <t xml:space="preserve">עובדיה מברטנורא</t>
         </is>
       </c>
       <c r="D16" s="65">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="E16" s="65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="F16">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G16" s="65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H16">
         <is>
-          <t xml:space="preserve">678מ״ר</t>
+          <t xml:space="preserve">80מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I16">
         <is>
-          <t xml:space="preserve">מרפסת: 86מ״ר</t>
+          <t xml:space="preserve">מרפסת: 6מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J16">
@@ -1230,13 +1227,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L16">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+      <c t="inlineStr" r="N16">
+        <is>
+          <t xml:space="preserve">דני נמדר</t>
         </is>
       </c>
       <c r="O16" s="63">
-        <v>60000000</v>
+        <v>4100000</v>
       </c>
       <c t="inlineStr" r="R16">
         <is>
@@ -1245,7 +1242,7 @@
       </c>
       <c t="inlineStr" r="S16">
         <is>
-          <t xml:space="preserve">אורן כהן26-09-2024</t>
+          <t xml:space="preserve">אין שיוך לאיש מכירות15-02-2026</t>
         </is>
       </c>
     </row>
@@ -1264,14 +1261,14 @@
         </is>
       </c>
       <c r="D17" s="65">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="E17" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F17">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">בית פרטי</t>
         </is>
       </c>
       <c r="G17" s="65">
@@ -1279,7 +1276,12 @@
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">100מ״ר</t>
+          <t xml:space="preserve">678מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I17">
+        <is>
+          <t xml:space="preserve">מרפסת: 86מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
@@ -1292,13 +1294,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="N17">
-        <is>
-          <t xml:space="preserve">תהילה נדב - מתווכת+972504205333</t>
-        </is>
-      </c>
-      <c r="O17" s="65">
-        <v>100</v>
+      <c t="inlineStr" r="L17">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c r="O17" s="63">
+        <v>60000000</v>
       </c>
       <c t="inlineStr" r="R17">
         <is>
@@ -1307,7 +1309,7 @@
       </c>
       <c t="inlineStr" r="S17">
         <is>
-          <t xml:space="preserve">אין שיוך לאיש מכירות16-02-2026</t>
+          <t xml:space="preserve">אורן כהן26-09-2024</t>
         </is>
       </c>
     </row>
@@ -1328,10 +1330,8 @@
       <c r="D18" s="65">
         <v>53</v>
       </c>
-      <c t="inlineStr" r="E18">
-        <is>
-          <t xml:space="preserve">/33</t>
-        </is>
+      <c r="E18" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F18">
         <is>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="G18" s="65">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H18">
         <is>
@@ -1371,7 +1371,7 @@
       </c>
       <c t="inlineStr" r="S18">
         <is>
-          <t xml:space="preserve">מנחם אוריאל16-02-2026</t>
+          <t xml:space="preserve">אין שיוך לאיש מכירות16-02-2026</t>
         </is>
       </c>
     </row>
@@ -1386,14 +1386,16 @@
       </c>
       <c t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">עזרת ישראל</t>
+          <t xml:space="preserve">עזה</t>
         </is>
       </c>
       <c r="D19" s="65">
-        <v>11</v>
-      </c>
-      <c r="E19" s="65">
-        <v>0</v>
+        <v>53</v>
+      </c>
+      <c t="inlineStr" r="E19">
+        <is>
+          <t xml:space="preserve">/33</t>
+        </is>
       </c>
       <c t="inlineStr" r="F19">
         <is>
@@ -1405,12 +1407,7 @@
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">215מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I19">
-        <is>
-          <t xml:space="preserve">מרפסת: 16מ״ר</t>
+          <t xml:space="preserve">100מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
@@ -1425,11 +1422,11 @@
       </c>
       <c t="inlineStr" r="N19">
         <is>
-          <t xml:space="preserve">ווין(054) 441-4566</t>
+          <t xml:space="preserve">תהילה נדב - מתווכת+972504205333</t>
         </is>
       </c>
       <c r="O19" s="65">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1438,7 +1435,7 @@
       </c>
       <c t="inlineStr" r="S19">
         <is>
-          <t xml:space="preserve">משה קולטון04-11-2024</t>
+          <t xml:space="preserve">מנחם אוריאל16-02-2026</t>
         </is>
       </c>
     </row>
@@ -1453,33 +1450,31 @@
       </c>
       <c t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">עליאש</t>
+          <t xml:space="preserve">עזרת ישראל</t>
         </is>
       </c>
       <c r="D20" s="65">
-        <v>6</v>
-      </c>
-      <c t="inlineStr" r="E20">
-        <is>
-          <t xml:space="preserve">/55</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="E20" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F20">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G20" s="65">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">300מ״ר</t>
+          <t xml:space="preserve">215מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I20">
         <is>
-          <t xml:space="preserve">מרפסת: 160מ״רמרפסת: 16מ״ר</t>
+          <t xml:space="preserve">מרפסת: 16מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
@@ -1492,18 +1487,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L20">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N20">
         <is>
-          <t xml:space="preserve">Mikael Rapaport</t>
-        </is>
-      </c>
-      <c r="O20" s="63">
-        <v>23000000</v>
+          <t xml:space="preserve">ווין(054) 441-4566</t>
+        </is>
+      </c>
+      <c r="O20" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1512,7 +1502,7 @@
       </c>
       <c t="inlineStr" r="S20">
         <is>
-          <t xml:space="preserve">אריה טאו23-10-2025</t>
+          <t xml:space="preserve">משה קולטון04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1527,26 +1517,33 @@
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">עמק רפאים</t>
+          <t xml:space="preserve">עליאש</t>
         </is>
       </c>
       <c r="D21" s="65">
-        <v>24</v>
-      </c>
-      <c r="E21" s="65">
-        <v>0</v>
+        <v>6</v>
+      </c>
+      <c t="inlineStr" r="E21">
+        <is>
+          <t xml:space="preserve">/55</t>
+        </is>
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G21" s="65">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">133מ״ר</t>
+          <t xml:space="preserve">300מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I21">
+        <is>
+          <t xml:space="preserve">מרפסת: 160מ״רמרפסת: 16מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
@@ -1559,13 +1556,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L21">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N21">
         <is>
-          <t xml:space="preserve">מורין פיין(050) 766-6063יניב פיין(058) 666-2230</t>
+          <t xml:space="preserve">Mikael Rapaport</t>
         </is>
       </c>
       <c r="O21" s="63">
-        <v>5700000</v>
+        <v>23000000</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1574,7 +1576,7 @@
       </c>
       <c t="inlineStr" r="S21">
         <is>
-          <t xml:space="preserve">אין שיוך לאיש מכירות19-06-2024</t>
+          <t xml:space="preserve">אריה טאו23-10-2025</t>
         </is>
       </c>
     </row>
@@ -1589,16 +1591,14 @@
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">פארן</t>
+          <t xml:space="preserve">עמק רפאים</t>
         </is>
       </c>
       <c r="D22" s="65">
-        <v>14</v>
-      </c>
-      <c t="inlineStr" r="E22">
-        <is>
-          <t xml:space="preserve">/44</t>
-        </is>
+        <v>24</v>
+      </c>
+      <c r="E22" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F22">
         <is>
@@ -1606,30 +1606,30 @@
         </is>
       </c>
       <c r="G22" s="65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t xml:space="preserve">82מ״ר</t>
+          <t xml:space="preserve">133מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K22">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N22">
         <is>
-          <t xml:space="preserve">רפאל(054) 736-1874</t>
+          <t xml:space="preserve">מורין פיין(050) 766-6063יניב פיין(058) 666-2230</t>
         </is>
       </c>
       <c r="O22" s="63">
-        <v>4800000</v>
+        <v>5700000</v>
       </c>
       <c t="inlineStr" r="R22">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c t="inlineStr" r="S22">
         <is>
-          <t xml:space="preserve">מירי רענן18-11-2024</t>
+          <t xml:space="preserve">אין שיוך לאיש מכירות19-06-2024</t>
         </is>
       </c>
     </row>
@@ -1653,50 +1653,47 @@
       </c>
       <c t="inlineStr" r="C23">
         <is>
-          <t xml:space="preserve">קורא הדורות</t>
+          <t xml:space="preserve">פארן</t>
         </is>
       </c>
       <c r="D23" s="65">
-        <v>49</v>
-      </c>
-      <c r="E23" s="65">
-        <v>6</v>
+        <v>14</v>
+      </c>
+      <c t="inlineStr" r="E23">
+        <is>
+          <t xml:space="preserve">/44</t>
+        </is>
       </c>
       <c t="inlineStr" r="F23">
         <is>
-          <t xml:space="preserve">דופלקס</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G23" s="65">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">187מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I23">
-        <is>
-          <t xml:space="preserve">מרפסת: 30מ״ר</t>
+          <t xml:space="preserve">82מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K23">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N23">
         <is>
-          <t xml:space="preserve">יוני אשהיים - מתווך054-4757543</t>
+          <t xml:space="preserve">רפאל(054) 736-1874</t>
         </is>
       </c>
       <c r="O23" s="63">
-        <v>5990000</v>
+        <v>4800000</v>
       </c>
       <c t="inlineStr" r="R23">
         <is>
@@ -1705,7 +1702,7 @@
       </c>
       <c t="inlineStr" r="S23">
         <is>
-          <t xml:space="preserve">מנחם אוריאל12-02-2026</t>
+          <t xml:space="preserve">מירי רענן18-11-2024</t>
         </is>
       </c>
     </row>
@@ -1720,31 +1717,31 @@
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">קליין</t>
+          <t xml:space="preserve">קורא הדורות</t>
         </is>
       </c>
       <c r="D24" s="65">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="E24" s="65">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
+          <t xml:space="preserve">דופלקס</t>
         </is>
       </c>
       <c r="G24" s="65">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="H24">
         <is>
-          <t xml:space="preserve">850מ״ר</t>
+          <t xml:space="preserve">187מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">מרפסת: 85מ״רגינה: 205מ״ר</t>
+          <t xml:space="preserve">מרפסת: 30מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
@@ -1757,23 +1754,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L24">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N24">
         <is>
-          <t xml:space="preserve">יותם בר חמה(054) 462-2020</t>
+          <t xml:space="preserve">יוני אשהיים - מתווך054-4757543</t>
         </is>
       </c>
       <c r="O24" s="63">
-        <v>100000000</v>
-      </c>
-      <c t="inlineStr" r="P24">
-        <is>
-          <t xml:space="preserve">בניין חדש</t>
-        </is>
+        <v>5990000</v>
       </c>
       <c t="inlineStr" r="R24">
         <is>
@@ -1782,7 +1769,7 @@
       </c>
       <c t="inlineStr" r="S24">
         <is>
-          <t xml:space="preserve">אורן כהן30-07-2024</t>
+          <t xml:space="preserve">מנחם אוריאל12-02-2026</t>
         </is>
       </c>
     </row>
@@ -1797,43 +1784,41 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">קנאי הגליל</t>
+          <t xml:space="preserve">קליין</t>
         </is>
       </c>
       <c r="D25" s="65">
-        <v>9</v>
-      </c>
-      <c t="inlineStr" r="E25">
-        <is>
-          <t xml:space="preserve">/88</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="E25" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
-        </is>
-      </c>
-      <c t="n" r="G25">
-        <v>5.5</v>
+          <t xml:space="preserve">בית פרטי</t>
+        </is>
+      </c>
+      <c r="G25" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">198מ״ר</t>
+          <t xml:space="preserve">850מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I25">
         <is>
-          <t xml:space="preserve">מרפסת: 109מ״רמרפסת: 11מ״ר</t>
+          <t xml:space="preserve">מרפסת: 85מ״רגינה: 205מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K25">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="L25">
@@ -1841,18 +1826,18 @@
           <t xml:space="preserve">צפון דרום מזרח מערב</t>
         </is>
       </c>
-      <c t="inlineStr" r="M25">
-        <is>
-          <t xml:space="preserve">חזית עורף</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N25">
         <is>
-          <t xml:space="preserve">מאיר אבוחצירא(058) 758-8139</t>
+          <t xml:space="preserve">יותם בר חמה(054) 462-2020</t>
         </is>
       </c>
       <c r="O25" s="63">
-        <v>12000000</v>
+        <v>100000000</v>
+      </c>
+      <c t="inlineStr" r="P25">
+        <is>
+          <t xml:space="preserve">בניין חדש</t>
+        </is>
       </c>
       <c t="inlineStr" r="R25">
         <is>
@@ -1861,7 +1846,7 @@
       </c>
       <c t="inlineStr" r="S25">
         <is>
-          <t xml:space="preserve">אריה טאו17-12-2025</t>
+          <t xml:space="preserve">אורן כהן30-07-2024</t>
         </is>
       </c>
     </row>
@@ -1876,45 +1861,62 @@
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">קרית משה</t>
+          <t xml:space="preserve">קנאי הגליל</t>
         </is>
       </c>
       <c r="D26" s="65">
-        <v>7</v>
-      </c>
-      <c r="E26" s="65">
-        <v>0</v>
+        <v>9</v>
+      </c>
+      <c t="inlineStr" r="E26">
+        <is>
+          <t xml:space="preserve">/88</t>
+        </is>
       </c>
       <c t="inlineStr" r="F26">
         <is>
           <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
-      <c r="G26" s="65">
-        <v>2</v>
+      <c t="n" r="G26">
+        <v>5.5</v>
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">97מ״ר</t>
+          <t xml:space="preserve">198מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I26">
+        <is>
+          <t xml:space="preserve">מרפסת: 109מ״רמרפסת: 11מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K26">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L26">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M26">
+        <is>
+          <t xml:space="preserve">חזית עורף</t>
         </is>
       </c>
       <c t="inlineStr" r="N26">
         <is>
-          <t xml:space="preserve">שילת דוד(054) 427-6001</t>
-        </is>
-      </c>
-      <c r="O26" s="65">
-        <v>0</v>
+          <t xml:space="preserve">מאיר אבוחצירא(058) 758-8139</t>
+        </is>
+      </c>
+      <c r="O26" s="63">
+        <v>12000000</v>
       </c>
       <c t="inlineStr" r="R26">
         <is>
@@ -1923,7 +1925,7 @@
       </c>
       <c t="inlineStr" r="S26">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">אריה טאו17-12-2025</t>
         </is>
       </c>
     </row>
@@ -1938,33 +1940,26 @@
       </c>
       <c t="inlineStr" r="C27">
         <is>
-          <t xml:space="preserve">קרן היסוד</t>
+          <t xml:space="preserve">קרית משה</t>
         </is>
       </c>
       <c r="D27" s="65">
-        <v>8</v>
-      </c>
-      <c t="inlineStr" r="E27">
-        <is>
-          <t xml:space="preserve">/32</t>
-        </is>
+        <v>7</v>
+      </c>
+      <c r="E27" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G27" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">70מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I27">
-        <is>
-          <t xml:space="preserve">מרפסת: 8מ״רמרפסת: 7מ״ר</t>
+          <t xml:space="preserve">97מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
@@ -1977,18 +1972,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L27">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N27">
         <is>
-          <t xml:space="preserve">סיימון סינגר</t>
-        </is>
-      </c>
-      <c r="O27" s="63">
-        <v>4300000</v>
+          <t xml:space="preserve">שילת דוד(054) 427-6001</t>
+        </is>
+      </c>
+      <c r="O27" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R27">
         <is>
@@ -1997,7 +1987,7 @@
       </c>
       <c t="inlineStr" r="S27">
         <is>
-          <t xml:space="preserve">מיכאל בלוך31-10-2024</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
